--- a/student_assistance_and_leaders.xlsx
+++ b/student_assistance_and_leaders.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,7 +509,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>112</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>116</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6">
@@ -587,7 +587,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7">
@@ -613,7 +613,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9">
@@ -665,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>152</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11">
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>139</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>112</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15">
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16">
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>116</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17">
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18">
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19">
@@ -925,7 +925,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20">
@@ -951,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>152</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21">
@@ -977,7 +977,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22">
@@ -1003,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>139</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23">
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24">
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>112</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26">
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27">
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>116</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28">
@@ -1159,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29">
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30">
@@ -1211,7 +1211,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31">
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>152</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32">
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33">
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>139</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34">
@@ -1315,7 +1315,33 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>113</v>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Test U.</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>157</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Student Assistance</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
